--- a/public/Template.xlsx
+++ b/public/Template.xlsx
@@ -569,7 +569,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:DA93"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35.17"/>
@@ -5809,355 +5809,355 @@
         <v>79</v>
       </c>
       <c r="C84" s="17" t="n">
-        <f aca="false">SUM(C79:C83)</f>
+        <f aca="false">SUM(C79,-C80,C81:C83)</f>
         <v>0</v>
       </c>
       <c r="D84" s="17" t="n">
-        <f aca="false">SUM(D79:D83)</f>
+        <f aca="false">SUM(D79,-D80,D81:D83)</f>
         <v>0</v>
       </c>
       <c r="E84" s="17" t="n">
-        <f aca="false">SUM(E79:E83)</f>
+        <f aca="false">SUM(E79,-E80,E81:E83)</f>
         <v>0</v>
       </c>
       <c r="F84" s="17" t="n">
-        <f aca="false">SUM(F79:F83)</f>
+        <f aca="false">SUM(F79,-F80,F81:F83)</f>
         <v>0</v>
       </c>
       <c r="G84" s="17" t="n">
-        <f aca="false">SUM(G79:G83)</f>
+        <f aca="false">SUM(G79,-G80,G81:G83)</f>
         <v>0</v>
       </c>
       <c r="H84" s="17" t="n">
-        <f aca="false">SUM(H79:H83)</f>
+        <f aca="false">SUM(H79,-H80,H81:H83)</f>
         <v>0</v>
       </c>
       <c r="I84" s="17" t="n">
-        <f aca="false">SUM(I79:I83)</f>
+        <f aca="false">SUM(I79,-I80,I81:I83)</f>
         <v>0</v>
       </c>
       <c r="J84" s="17" t="n">
-        <f aca="false">SUM(J79:J83)</f>
+        <f aca="false">SUM(J79,-J80,J81:J83)</f>
         <v>0</v>
       </c>
       <c r="K84" s="17" t="n">
-        <f aca="false">SUM(K79:K83)</f>
+        <f aca="false">SUM(K79,-K80,K81:K83)</f>
         <v>0</v>
       </c>
       <c r="L84" s="17" t="n">
-        <f aca="false">SUM(L79:L83)</f>
+        <f aca="false">SUM(L79,-L80,L81:L83)</f>
         <v>0</v>
       </c>
       <c r="M84" s="17" t="n">
-        <f aca="false">SUM(M79:M83)</f>
+        <f aca="false">SUM(M79,-M80,M81:M83)</f>
         <v>0</v>
       </c>
       <c r="N84" s="17" t="n">
-        <f aca="false">SUM(N79:N83)</f>
+        <f aca="false">SUM(N79,-N80,N81:N83)</f>
         <v>0</v>
       </c>
       <c r="O84" s="17" t="n">
-        <f aca="false">SUM(O79:O83)</f>
+        <f aca="false">SUM(O79,-O80,O81:O83)</f>
         <v>0</v>
       </c>
       <c r="P84" s="17" t="n">
-        <f aca="false">SUM(P79:P83)</f>
+        <f aca="false">SUM(P79,-P80,P81:P83)</f>
         <v>0</v>
       </c>
       <c r="Q84" s="17" t="n">
-        <f aca="false">SUM(Q79:Q83)</f>
+        <f aca="false">SUM(Q79,-Q80,Q81:Q83)</f>
         <v>0</v>
       </c>
       <c r="R84" s="17" t="n">
-        <f aca="false">SUM(R79:R83)</f>
+        <f aca="false">SUM(R79,-R80,R81:R83)</f>
         <v>0</v>
       </c>
       <c r="S84" s="17" t="n">
-        <f aca="false">SUM(S79:S83)</f>
+        <f aca="false">SUM(S79,-S80,S81:S83)</f>
         <v>0</v>
       </c>
       <c r="T84" s="17" t="n">
-        <f aca="false">SUM(T79:T83)</f>
+        <f aca="false">SUM(T79,-T80,T81:T83)</f>
         <v>0</v>
       </c>
       <c r="U84" s="17" t="n">
-        <f aca="false">SUM(U79:U83)</f>
+        <f aca="false">SUM(U79,-U80,U81:U83)</f>
         <v>0</v>
       </c>
       <c r="V84" s="17" t="n">
-        <f aca="false">SUM(V79:V83)</f>
+        <f aca="false">SUM(V79,-V80,V81:V83)</f>
         <v>0</v>
       </c>
       <c r="W84" s="17" t="n">
-        <f aca="false">SUM(W79:W83)</f>
+        <f aca="false">SUM(W79,-W80,W81:W83)</f>
         <v>0</v>
       </c>
       <c r="X84" s="17" t="n">
-        <f aca="false">SUM(X79:X83)</f>
+        <f aca="false">SUM(X79,-X80,X81:X83)</f>
         <v>0</v>
       </c>
       <c r="Y84" s="17" t="n">
-        <f aca="false">SUM(Y79:Y83)</f>
+        <f aca="false">SUM(Y79,-Y80,Y81:Y83)</f>
         <v>0</v>
       </c>
       <c r="Z84" s="17" t="n">
-        <f aca="false">SUM(Z79:Z83)</f>
+        <f aca="false">SUM(Z79,-Z80,Z81:Z83)</f>
         <v>0</v>
       </c>
       <c r="AA84" s="17" t="n">
-        <f aca="false">SUM(AA79:AA83)</f>
+        <f aca="false">SUM(AA79,-AA80,AA81:AA83)</f>
         <v>0</v>
       </c>
       <c r="AB84" s="17" t="n">
-        <f aca="false">SUM(AB79:AB83)</f>
+        <f aca="false">SUM(AB79,-AB80,AB81:AB83)</f>
         <v>0</v>
       </c>
       <c r="AC84" s="17" t="n">
-        <f aca="false">SUM(AC79:AC83)</f>
+        <f aca="false">SUM(AC79,-AC80,AC81:AC83)</f>
         <v>0</v>
       </c>
       <c r="AD84" s="17" t="n">
-        <f aca="false">SUM(AD79:AD83)</f>
+        <f aca="false">SUM(AD79,-AD80,AD81:AD83)</f>
         <v>0</v>
       </c>
       <c r="AE84" s="17" t="n">
-        <f aca="false">SUM(AE79:AE83)</f>
+        <f aca="false">SUM(AE79,-AE80,AE81:AE83)</f>
         <v>0</v>
       </c>
       <c r="AF84" s="17" t="n">
-        <f aca="false">SUM(AF79:AF83)</f>
+        <f aca="false">SUM(AF79,-AF80,AF81:AF83)</f>
         <v>0</v>
       </c>
       <c r="AG84" s="17" t="n">
-        <f aca="false">SUM(AG79:AG83)</f>
+        <f aca="false">SUM(AG79,-AG80,AG81:AG83)</f>
         <v>0</v>
       </c>
       <c r="AH84" s="17" t="n">
-        <f aca="false">SUM(AH79:AH83)</f>
+        <f aca="false">SUM(AH79,-AH80,AH81:AH83)</f>
         <v>0</v>
       </c>
       <c r="AI84" s="17" t="n">
-        <f aca="false">SUM(AI79:AI83)</f>
+        <f aca="false">SUM(AI79,-AI80,AI81:AI83)</f>
         <v>0</v>
       </c>
       <c r="AJ84" s="17" t="n">
-        <f aca="false">SUM(AJ79:AJ83)</f>
+        <f aca="false">SUM(AJ79,-AJ80,AJ81:AJ83)</f>
         <v>0</v>
       </c>
       <c r="AK84" s="17" t="n">
-        <f aca="false">SUM(AK79:AK83)</f>
+        <f aca="false">SUM(AK79,-AK80,AK81:AK83)</f>
         <v>0</v>
       </c>
       <c r="AL84" s="17" t="n">
-        <f aca="false">SUM(AL79:AL83)</f>
+        <f aca="false">SUM(AL79,-AL80,AL81:AL83)</f>
         <v>0</v>
       </c>
       <c r="AM84" s="17" t="n">
-        <f aca="false">SUM(AM79:AM83)</f>
+        <f aca="false">SUM(AM79,-AM80,AM81:AM83)</f>
         <v>0</v>
       </c>
       <c r="AN84" s="17" t="n">
-        <f aca="false">SUM(AN79:AN83)</f>
+        <f aca="false">SUM(AN79,-AN80,AN81:AN83)</f>
         <v>0</v>
       </c>
       <c r="AO84" s="17" t="n">
-        <f aca="false">SUM(AO79:AO83)</f>
+        <f aca="false">SUM(AO79,-AO80,AO81:AO83)</f>
         <v>0</v>
       </c>
       <c r="AP84" s="17" t="n">
-        <f aca="false">SUM(AP79:AP83)</f>
+        <f aca="false">SUM(AP79,-AP80,AP81:AP83)</f>
         <v>0</v>
       </c>
       <c r="AQ84" s="17" t="n">
-        <f aca="false">SUM(AQ79:AQ83)</f>
+        <f aca="false">SUM(AQ79,-AQ80,AQ81:AQ83)</f>
         <v>0</v>
       </c>
       <c r="AR84" s="17" t="n">
-        <f aca="false">SUM(AR79:AR83)</f>
+        <f aca="false">SUM(AR79,-AR80,AR81:AR83)</f>
         <v>0</v>
       </c>
       <c r="AS84" s="17" t="n">
-        <f aca="false">SUM(AS79:AS83)</f>
+        <f aca="false">SUM(AS79,-AS80,AS81:AS83)</f>
         <v>0</v>
       </c>
       <c r="AT84" s="17" t="n">
-        <f aca="false">SUM(AT79:AT83)</f>
+        <f aca="false">SUM(AT79,-AT80,AT81:AT83)</f>
         <v>0</v>
       </c>
       <c r="AU84" s="17" t="n">
-        <f aca="false">SUM(AU79:AU83)</f>
+        <f aca="false">SUM(AU79,-AU80,AU81:AU83)</f>
         <v>0</v>
       </c>
       <c r="AV84" s="17" t="n">
-        <f aca="false">SUM(AV79:AV83)</f>
+        <f aca="false">SUM(AV79,-AV80,AV81:AV83)</f>
         <v>0</v>
       </c>
       <c r="AW84" s="17" t="n">
-        <f aca="false">SUM(AW79:AW83)</f>
+        <f aca="false">SUM(AW79,-AW80,AW81:AW83)</f>
         <v>0</v>
       </c>
       <c r="AX84" s="17" t="n">
-        <f aca="false">SUM(AX79:AX83)</f>
+        <f aca="false">SUM(AX79,-AX80,AX81:AX83)</f>
         <v>0</v>
       </c>
       <c r="AY84" s="17" t="n">
-        <f aca="false">SUM(AY79:AY83)</f>
+        <f aca="false">SUM(AY79,-AY80,AY81:AY83)</f>
         <v>0</v>
       </c>
       <c r="AZ84" s="17" t="n">
-        <f aca="false">SUM(AZ79:AZ83)</f>
+        <f aca="false">SUM(AZ79,-AZ80,AZ81:AZ83)</f>
         <v>0</v>
       </c>
       <c r="BA84" s="17" t="n">
-        <f aca="false">SUM(BA79:BA83)</f>
+        <f aca="false">SUM(BA79,-BA80,BA81:BA83)</f>
         <v>0</v>
       </c>
       <c r="BB84" s="17" t="n">
-        <f aca="false">SUM(BB79:BB83)</f>
+        <f aca="false">SUM(BB79,-BB80,BB81:BB83)</f>
         <v>0</v>
       </c>
       <c r="BC84" s="17" t="n">
-        <f aca="false">SUM(BC79:BC83)</f>
+        <f aca="false">SUM(BC79,-BC80,BC81:BC83)</f>
         <v>0</v>
       </c>
       <c r="BD84" s="17" t="n">
-        <f aca="false">SUM(BD79:BD83)</f>
+        <f aca="false">SUM(BD79,-BD80,BD81:BD83)</f>
         <v>0</v>
       </c>
       <c r="BE84" s="17" t="n">
-        <f aca="false">SUM(BE79:BE83)</f>
+        <f aca="false">SUM(BE79,-BE80,BE81:BE83)</f>
         <v>0</v>
       </c>
       <c r="BF84" s="17" t="n">
-        <f aca="false">SUM(BF79:BF83)</f>
+        <f aca="false">SUM(BF79,-BF80,BF81:BF83)</f>
         <v>0</v>
       </c>
       <c r="BG84" s="17" t="n">
-        <f aca="false">SUM(BG79:BG83)</f>
+        <f aca="false">SUM(BG79,-BG80,BG81:BG83)</f>
         <v>0</v>
       </c>
       <c r="BH84" s="17" t="n">
-        <f aca="false">SUM(BH79:BH83)</f>
+        <f aca="false">SUM(BH79,-BH80,BH81:BH83)</f>
         <v>0</v>
       </c>
       <c r="BI84" s="17" t="n">
-        <f aca="false">SUM(BI79:BI83)</f>
+        <f aca="false">SUM(BI79,-BI80,BI81:BI83)</f>
         <v>0</v>
       </c>
       <c r="BJ84" s="17" t="n">
-        <f aca="false">SUM(BJ79:BJ83)</f>
+        <f aca="false">SUM(BJ79,-BJ80,BJ81:BJ83)</f>
         <v>0</v>
       </c>
       <c r="BK84" s="17" t="n">
-        <f aca="false">SUM(BK79:BK83)</f>
+        <f aca="false">SUM(BK79,-BK80,BK81:BK83)</f>
         <v>0</v>
       </c>
       <c r="BL84" s="17" t="n">
-        <f aca="false">SUM(BL79:BL83)</f>
+        <f aca="false">SUM(BL79,-BL80,BL81:BL83)</f>
         <v>0</v>
       </c>
       <c r="BM84" s="17" t="n">
-        <f aca="false">SUM(BM79:BM83)</f>
+        <f aca="false">SUM(BM79,-BM80,BM81:BM83)</f>
         <v>0</v>
       </c>
       <c r="BN84" s="17" t="n">
-        <f aca="false">SUM(BN79:BN83)</f>
+        <f aca="false">SUM(BN79,-BN80,BN81:BN83)</f>
         <v>0</v>
       </c>
       <c r="BO84" s="17" t="n">
-        <f aca="false">SUM(BO79:BO83)</f>
+        <f aca="false">SUM(BO79,-BO80,BO81:BO83)</f>
         <v>0</v>
       </c>
       <c r="BP84" s="17" t="n">
-        <f aca="false">SUM(BP79:BP83)</f>
+        <f aca="false">SUM(BP79,-BP80,BP81:BP83)</f>
         <v>0</v>
       </c>
       <c r="BQ84" s="17" t="n">
-        <f aca="false">SUM(BQ79:BQ83)</f>
+        <f aca="false">SUM(BQ79,-BQ80,BQ81:BQ83)</f>
         <v>0</v>
       </c>
       <c r="BR84" s="17" t="n">
-        <f aca="false">SUM(BR79:BR83)</f>
+        <f aca="false">SUM(BR79,-BR80,BR81:BR83)</f>
         <v>0</v>
       </c>
       <c r="BS84" s="17" t="n">
-        <f aca="false">SUM(BS79:BS83)</f>
+        <f aca="false">SUM(BS79,-BS80,BS81:BS83)</f>
         <v>0</v>
       </c>
       <c r="BT84" s="17" t="n">
-        <f aca="false">SUM(BT79:BT83)</f>
+        <f aca="false">SUM(BT79,-BT80,BT81:BT83)</f>
         <v>0</v>
       </c>
       <c r="BU84" s="17" t="n">
-        <f aca="false">SUM(BU79:BU83)</f>
+        <f aca="false">SUM(BU79,-BU80,BU81:BU83)</f>
         <v>0</v>
       </c>
       <c r="BV84" s="17" t="n">
-        <f aca="false">SUM(BV79:BV83)</f>
+        <f aca="false">SUM(BV79,-BV80,BV81:BV83)</f>
         <v>0</v>
       </c>
       <c r="BW84" s="17" t="n">
-        <f aca="false">SUM(BW79:BW83)</f>
+        <f aca="false">SUM(BW79,-BW80,BW81:BW83)</f>
         <v>0</v>
       </c>
       <c r="BX84" s="17" t="n">
-        <f aca="false">SUM(BX79:BX83)</f>
+        <f aca="false">SUM(BX79,-BX80,BX81:BX83)</f>
         <v>0</v>
       </c>
       <c r="BY84" s="17" t="n">
-        <f aca="false">SUM(BY79:BY83)</f>
+        <f aca="false">SUM(BY79,-BY80,BY81:BY83)</f>
         <v>0</v>
       </c>
       <c r="BZ84" s="17" t="n">
-        <f aca="false">SUM(BZ79:BZ83)</f>
+        <f aca="false">SUM(BZ79,-BZ80,BZ81:BZ83)</f>
         <v>0</v>
       </c>
       <c r="CA84" s="17" t="n">
-        <f aca="false">SUM(CA79:CA83)</f>
+        <f aca="false">SUM(CA79,-CA80,CA81:CA83)</f>
         <v>0</v>
       </c>
       <c r="CB84" s="17" t="n">
-        <f aca="false">SUM(CB79:CB83)</f>
+        <f aca="false">SUM(CB79,-CB80,CB81:CB83)</f>
         <v>0</v>
       </c>
       <c r="CC84" s="17" t="n">
-        <f aca="false">SUM(CC79:CC83)</f>
+        <f aca="false">SUM(CC79,-CC80,CC81:CC83)</f>
         <v>0</v>
       </c>
       <c r="CD84" s="17" t="n">
-        <f aca="false">SUM(CD79:CD83)</f>
+        <f aca="false">SUM(CD79,-CD80,CD81:CD83)</f>
         <v>0</v>
       </c>
       <c r="CE84" s="17" t="n">
-        <f aca="false">SUM(CE79:CE83)</f>
+        <f aca="false">SUM(CE79,-CE80,CE81:CE83)</f>
         <v>0</v>
       </c>
       <c r="CF84" s="17" t="n">
-        <f aca="false">SUM(CF79:CF83)</f>
+        <f aca="false">SUM(CF79,-CF80,CF81:CF83)</f>
         <v>0</v>
       </c>
       <c r="CG84" s="17" t="n">
-        <f aca="false">SUM(CG79:CG83)</f>
+        <f aca="false">SUM(CG79,-CG80,CG81:CG83)</f>
         <v>0</v>
       </c>
       <c r="CH84" s="17" t="n">
-        <f aca="false">SUM(CH79:CH83)</f>
+        <f aca="false">SUM(CH79,-CH80,CH81:CH83)</f>
         <v>0</v>
       </c>
       <c r="CI84" s="17" t="n">
-        <f aca="false">SUM(CI79:CI83)</f>
+        <f aca="false">SUM(CI79,-CI80,CI81:CI83)</f>
         <v>0</v>
       </c>
       <c r="CJ84" s="17" t="n">
-        <f aca="false">SUM(CJ79:CJ83)</f>
+        <f aca="false">SUM(CJ79,-CJ80,CJ81:CJ83)</f>
         <v>0</v>
       </c>
       <c r="CK84" s="17" t="n">
-        <f aca="false">SUM(CK79:CK83)</f>
+        <f aca="false">SUM(CK79,-CK80,CK81:CK83)</f>
         <v>0</v>
       </c>
       <c r="CL84" s="17" t="n">
-        <f aca="false">SUM(CL79:CL83)</f>
+        <f aca="false">SUM(CL79,-CL80,CL81:CL83)</f>
         <v>0</v>
       </c>
     </row>

--- a/public/Template.xlsx
+++ b/public/Template.xlsx
@@ -569,7 +569,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:DA93"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35.17"/>
